--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241025120000</t>
+    <t>20241209120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T12:00:00+01:00</t>
+    <t>2024-12-09T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
     <t>127</t>
   </si>
   <si>
-    <t>Réanimation médico-chirurgicale (polyvalente)</t>
+    <t>Réanimation polyvalente</t>
   </si>
   <si>
     <t>128</t>
@@ -1836,7 +1836,7 @@
     <t>351</t>
   </si>
   <si>
-    <t>Soins intensifs médico-chirurgicaux (polyvalent)</t>
+    <t>Soins intensifs polyvalents</t>
   </si>
   <si>
     <t>352</t>
@@ -1962,7 +1962,7 @@
     <t>373</t>
   </si>
   <si>
-    <t>Surveillance continue médico-chirurgicale (polyvalente)</t>
+    <t>Surveillance continue polyvalente</t>
   </si>
   <si>
     <t>374</t>
@@ -2250,7 +2250,7 @@
     <t>426</t>
   </si>
   <si>
-    <t>Kinésithérapie orientation Lésions cutanées et cicatrices (dermatologie)</t>
+    <t>Kinésithérapie orientation Lésions cutanées et cicatrices (dermatologie, brûlés)</t>
   </si>
   <si>
     <t>427</t>
